--- a/salidas/empresas/ZTS.xlsx
+++ b/salidas/empresas/ZTS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B2" t="n">
-        <v>29.77680778503418</v>
+        <v>29.77680206298828</v>
       </c>
       <c r="C2" t="n">
         <v>33.45000076293945</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B3" t="n">
-        <v>29.73231506347656</v>
+        <v>29.73230934143066</v>
       </c>
       <c r="C3" t="n">
         <v>33.40000152587891</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B4" t="n">
-        <v>29.45268821716309</v>
+        <v>29.45268440246582</v>
       </c>
       <c r="C4" t="n">
         <v>33.02000045776367</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B5" t="n">
-        <v>28.54287719726562</v>
+        <v>28.54287528991699</v>
       </c>
       <c r="C5" t="n">
         <v>32</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B6" t="n">
-        <v>27.55278968811035</v>
+        <v>27.55279922485352</v>
       </c>
       <c r="C6" t="n">
         <v>30.88999938964844</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B7" t="n">
-        <v>26.64703750610352</v>
+        <v>26.64703178405762</v>
       </c>
       <c r="C7" t="n">
         <v>29.80999946594238</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B8" t="n">
-        <v>26.05706405639648</v>
+        <v>26.05705070495605</v>
       </c>
       <c r="C8" t="n">
         <v>29.14999961853027</v>
@@ -621,11 +633,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B9" t="n">
-        <v>27.81803894042969</v>
+        <v>27.81802940368652</v>
       </c>
       <c r="C9" t="n">
         <v>31.1200008392334</v>
@@ -646,7 +658,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B10" t="n">
@@ -671,11 +683,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B11" t="n">
-        <v>27.90147972106934</v>
+        <v>27.90147399902344</v>
       </c>
       <c r="C11" t="n">
         <v>31.14999961853027</v>
@@ -696,11 +708,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B12" t="n">
-        <v>29.28087043762207</v>
+        <v>29.28086471557617</v>
       </c>
       <c r="C12" t="n">
         <v>32.68999862670898</v>
@@ -721,7 +733,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B13" t="n">
@@ -746,11 +758,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B14" t="n">
-        <v>27.84897613525391</v>
+        <v>27.8489818572998</v>
       </c>
       <c r="C14" t="n">
         <v>31.02000045776367</v>
@@ -771,11 +783,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B15" t="n">
-        <v>25.98159980773926</v>
+        <v>25.98159408569336</v>
       </c>
       <c r="C15" t="n">
         <v>28.94000053405762</v>
@@ -800,7 +812,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B16" t="n">
@@ -829,11 +841,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B17" t="n">
-        <v>27.62937545776367</v>
+        <v>27.62937355041504</v>
       </c>
       <c r="C17" t="n">
         <v>30.70000076293945</v>
@@ -858,11 +870,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B18" t="n">
-        <v>29.04234504699707</v>
+        <v>29.04233741760254</v>
       </c>
       <c r="C18" t="n">
         <v>32.27000045776367</v>
@@ -887,11 +899,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B19" t="n">
-        <v>29.61832237243652</v>
+        <v>29.61833000183105</v>
       </c>
       <c r="C19" t="n">
         <v>32.90999984741211</v>
@@ -916,11 +928,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B20" t="n">
-        <v>31.96359825134277</v>
+        <v>31.96357917785645</v>
       </c>
       <c r="C20" t="n">
         <v>35.43999862670898</v>
@@ -945,11 +957,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B21" t="n">
-        <v>33.32545852661133</v>
+        <v>33.32546234130859</v>
       </c>
       <c r="C21" t="n">
         <v>36.95000076293945</v>
@@ -974,7 +986,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B22" t="n">
@@ -1003,11 +1015,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B23" t="n">
-        <v>40.60134887695312</v>
+        <v>40.60134506225586</v>
       </c>
       <c r="C23" t="n">
         <v>44.93000030517578</v>
@@ -1032,11 +1044,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B24" t="n">
-        <v>38.88440704345703</v>
+        <v>38.88440322875977</v>
       </c>
       <c r="C24" t="n">
         <v>43.02999877929688</v>
@@ -1061,11 +1073,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B25" t="n">
-        <v>38.6859130859375</v>
+        <v>38.6859245300293</v>
       </c>
       <c r="C25" t="n">
         <v>42.72999954223633</v>
@@ -1090,11 +1102,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B26" t="n">
-        <v>41.72792434692383</v>
+        <v>41.72791290283203</v>
       </c>
       <c r="C26" t="n">
         <v>46.09000015258789</v>
@@ -1119,11 +1131,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B27" t="n">
-        <v>41.90899276733398</v>
+        <v>41.90898513793945</v>
       </c>
       <c r="C27" t="n">
         <v>46.29000091552734</v>
@@ -1148,11 +1160,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B28" t="n">
-        <v>40.28814697265625</v>
+        <v>40.28813934326172</v>
       </c>
       <c r="C28" t="n">
         <v>44.41999816894531</v>
@@ -1177,11 +1189,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B29" t="n">
-        <v>45.1404914855957</v>
+        <v>45.14049911499023</v>
       </c>
       <c r="C29" t="n">
         <v>49.77000045776367</v>
@@ -1206,11 +1218,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B30" t="n">
-        <v>43.73467636108398</v>
+        <v>43.73467254638672</v>
       </c>
       <c r="C30" t="n">
         <v>48.22000122070312</v>
@@ -1235,11 +1247,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B31" t="n">
-        <v>44.42398071289062</v>
+        <v>44.42397308349609</v>
       </c>
       <c r="C31" t="n">
         <v>48.97999954223633</v>
@@ -1264,11 +1276,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B32" t="n">
-        <v>40.76621246337891</v>
+        <v>40.76620864868164</v>
       </c>
       <c r="C32" t="n">
         <v>44.86999893188477</v>
@@ -1293,11 +1305,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B33" t="n">
-        <v>37.41370010375977</v>
+        <v>37.4136962890625</v>
       </c>
       <c r="C33" t="n">
         <v>41.18000030517578</v>
@@ -1322,11 +1334,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B34" t="n">
-        <v>39.07632446289062</v>
+        <v>39.07632064819336</v>
       </c>
       <c r="C34" t="n">
         <v>43.0099983215332</v>
@@ -1351,11 +1363,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B35" t="n">
-        <v>42.50857925415039</v>
+        <v>42.50857162475586</v>
       </c>
       <c r="C35" t="n">
         <v>46.70000076293945</v>
@@ -1380,11 +1392,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B36" t="n">
-        <v>43.61909484863281</v>
+        <v>43.61908721923828</v>
       </c>
       <c r="C36" t="n">
         <v>47.91999816894531</v>
@@ -1409,7 +1421,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B37" t="n">
@@ -1438,11 +1450,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B38" t="n">
-        <v>37.45682144165039</v>
+        <v>37.45680999755859</v>
       </c>
       <c r="C38" t="n">
         <v>41.06000137329102</v>
@@ -1467,11 +1479,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B39" t="n">
-        <v>40.43986892700195</v>
+        <v>40.43986511230469</v>
       </c>
       <c r="C39" t="n">
         <v>44.33000183105469</v>
@@ -1496,11 +1508,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B40" t="n">
-        <v>42.99217224121094</v>
+        <v>42.9921875</v>
       </c>
       <c r="C40" t="n">
         <v>47.02999877929688</v>
@@ -1525,7 +1537,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B41" t="n">
@@ -1554,11 +1566,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B42" t="n">
-        <v>43.47618865966797</v>
+        <v>43.4761962890625</v>
       </c>
       <c r="C42" t="n">
         <v>47.45999908447266</v>
@@ -1583,11 +1595,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B43" t="n">
-        <v>46.2335319519043</v>
+        <v>46.23353576660156</v>
       </c>
       <c r="C43" t="n">
         <v>50.47000122070312</v>
@@ -1612,11 +1624,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B44" t="n">
-        <v>46.81064224243164</v>
+        <v>46.81064605712891</v>
       </c>
       <c r="C44" t="n">
         <v>51.09999847412109</v>
@@ -1641,11 +1653,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B45" t="n">
-        <v>47.64426803588867</v>
+        <v>47.64426040649414</v>
       </c>
       <c r="C45" t="n">
         <v>52.0099983215332</v>
@@ -1670,11 +1682,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B46" t="n">
-        <v>43.78766250610352</v>
+        <v>43.78765106201172</v>
       </c>
       <c r="C46" t="n">
         <v>47.79999923706055</v>
@@ -1699,7 +1711,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B47" t="n">
@@ -1728,7 +1740,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B48" t="n">
@@ -1757,7 +1769,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B49" t="n">
@@ -1786,11 +1798,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B50" t="n">
-        <v>49.02911758422852</v>
+        <v>49.02912521362305</v>
       </c>
       <c r="C50" t="n">
         <v>53.31000137329102</v>
@@ -1815,7 +1827,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B51" t="n">
@@ -1844,11 +1856,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B52" t="n">
-        <v>51.70639801025391</v>
+        <v>51.70639038085938</v>
       </c>
       <c r="C52" t="n">
         <v>56.11000061035156</v>
@@ -1873,11 +1885,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B53" t="n">
-        <v>57.39215087890625</v>
+        <v>57.39215469360352</v>
       </c>
       <c r="C53" t="n">
         <v>62.27999877929688</v>
@@ -1902,7 +1914,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B54" t="n">
@@ -1931,11 +1943,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B55" t="n">
-        <v>57.71129608154297</v>
+        <v>57.7112922668457</v>
       </c>
       <c r="C55" t="n">
         <v>62.52000045776367</v>
@@ -1960,11 +1972,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B56" t="n">
-        <v>57.8774528503418</v>
+        <v>57.87744522094727</v>
       </c>
       <c r="C56" t="n">
         <v>62.70000076293945</v>
@@ -1989,11 +2001,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B57" t="n">
-        <v>58.85591888427734</v>
+        <v>58.85591506958008</v>
       </c>
       <c r="C57" t="n">
         <v>63.7599983215332</v>
@@ -2018,7 +2030,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B58" t="n">
@@ -2047,11 +2059,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B59" t="n">
-        <v>66.83236694335938</v>
+        <v>66.83235931396484</v>
       </c>
       <c r="C59" t="n">
         <v>72.29000091552734</v>
@@ -2076,11 +2088,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B60" t="n">
-        <v>66.60122680664062</v>
+        <v>66.60121154785156</v>
       </c>
       <c r="C60" t="n">
         <v>72.04000091552734</v>
@@ -2105,7 +2117,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B61" t="n">
@@ -2134,11 +2146,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B62" t="n">
-        <v>74.87825775146484</v>
+        <v>74.87824249267578</v>
       </c>
       <c r="C62" t="n">
         <v>80.86000061035156</v>
@@ -2163,11 +2175,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B63" t="n">
-        <v>77.33222198486328</v>
+        <v>77.33222961425781</v>
       </c>
       <c r="C63" t="n">
         <v>83.51000213623047</v>
@@ -2192,11 +2204,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B64" t="n">
-        <v>77.41790771484375</v>
+        <v>77.41789245605469</v>
       </c>
       <c r="C64" t="n">
         <v>83.48000335693359</v>
@@ -2221,11 +2233,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B65" t="n">
-        <v>77.62191772460938</v>
+        <v>77.62193298339844</v>
       </c>
       <c r="C65" t="n">
         <v>83.69999694824219</v>
@@ -2250,11 +2262,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B66" t="n">
-        <v>79.00373077392578</v>
+        <v>79.00372314453125</v>
       </c>
       <c r="C66" t="n">
         <v>85.19000244140625</v>
@@ -2279,11 +2291,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B67" t="n">
-        <v>80.31781768798828</v>
+        <v>80.31779479980469</v>
       </c>
       <c r="C67" t="n">
         <v>86.48000335693359</v>
@@ -2308,11 +2320,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B68" t="n">
-        <v>84.14421081542969</v>
+        <v>84.14420318603516</v>
       </c>
       <c r="C68" t="n">
         <v>90.59999847412109</v>
@@ -2337,7 +2349,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B69" t="n">
@@ -2366,7 +2378,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B70" t="n">
@@ -2395,11 +2407,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B71" t="n">
-        <v>87.30042266845703</v>
+        <v>87.30043029785156</v>
       </c>
       <c r="C71" t="n">
         <v>93.87000274658203</v>
@@ -2424,11 +2436,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B72" t="n">
-        <v>79.55340576171875</v>
+        <v>79.55341339111328</v>
       </c>
       <c r="C72" t="n">
         <v>85.54000091552734</v>
@@ -2453,11 +2465,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B73" t="n">
-        <v>80.28826904296875</v>
+        <v>80.28826141357422</v>
       </c>
       <c r="C73" t="n">
         <v>86.16000366210938</v>
@@ -2482,11 +2494,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B74" t="n">
-        <v>87.80829620361328</v>
+        <v>87.80828857421875</v>
       </c>
       <c r="C74" t="n">
         <v>94.23000335693359</v>
@@ -2511,11 +2523,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B75" t="n">
-        <v>93.80940246582031</v>
+        <v>93.80939483642578</v>
       </c>
       <c r="C75" t="n">
         <v>100.6699981689453</v>
@@ -2540,11 +2552,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B76" t="n">
-        <v>95.05685424804688</v>
+        <v>95.05686187744141</v>
       </c>
       <c r="C76" t="n">
         <v>101.8399963378906</v>
@@ -2569,11 +2581,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B77" t="n">
-        <v>94.31947326660156</v>
+        <v>94.31951141357422</v>
       </c>
       <c r="C77" t="n">
         <v>101.0500030517578</v>
@@ -2598,7 +2610,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B78" t="n">
@@ -2627,11 +2639,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B79" t="n">
-        <v>107.3926010131836</v>
+        <v>107.3925857543945</v>
       </c>
       <c r="C79" t="n">
         <v>114.8899993896484</v>
@@ -2656,11 +2668,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B80" t="n">
-        <v>118.1701889038086</v>
+        <v>118.1701812744141</v>
       </c>
       <c r="C80" t="n">
         <v>126.4199981689453</v>
@@ -2685,11 +2697,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B81" t="n">
-        <v>116.4595794677734</v>
+        <v>116.459587097168</v>
       </c>
       <c r="C81" t="n">
         <v>124.5899963378906</v>
@@ -2714,11 +2726,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B82" t="n">
-        <v>119.7255401611328</v>
+        <v>119.7255554199219</v>
       </c>
       <c r="C82" t="n">
         <v>127.9199981689453</v>
@@ -2743,11 +2755,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B83" t="n">
-        <v>112.799560546875</v>
+        <v>112.7995834350586</v>
       </c>
       <c r="C83" t="n">
         <v>120.5199966430664</v>
@@ -2772,11 +2784,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B84" t="n">
-        <v>123.8717651367188</v>
+        <v>123.8717803955078</v>
       </c>
       <c r="C84" t="n">
         <v>132.3500061035156</v>
@@ -2801,11 +2813,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B85" t="n">
-        <v>125.794189453125</v>
+        <v>125.7942199707031</v>
       </c>
       <c r="C85" t="n">
         <v>134.2100067138672</v>
@@ -2830,11 +2842,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B86" t="n">
-        <v>124.8756332397461</v>
+        <v>124.8756713867188</v>
       </c>
       <c r="C86" t="n">
         <v>133.2299957275391</v>
@@ -2859,7 +2871,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B87" t="n">
@@ -2888,11 +2900,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B88" t="n">
-        <v>121.3975830078125</v>
+        <v>121.3976058959961</v>
       </c>
       <c r="C88" t="n">
         <v>129.3099975585938</v>
@@ -2917,11 +2929,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B89" t="n">
-        <v>130.8607788085938</v>
+        <v>130.8607940673828</v>
       </c>
       <c r="C89" t="n">
         <v>139.3899993896484</v>
@@ -2946,11 +2958,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B90" t="n">
-        <v>128.6545867919922</v>
+        <v>128.6545715332031</v>
       </c>
       <c r="C90" t="n">
         <v>137.0399932861328</v>
@@ -2975,7 +2987,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B91" t="n">
@@ -3004,11 +3016,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B92" t="n">
-        <v>150.5142517089844</v>
+        <v>150.5141906738281</v>
       </c>
       <c r="C92" t="n">
         <v>160.1000061035156</v>
@@ -3033,11 +3045,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B93" t="n">
-        <v>155.4686279296875</v>
+        <v>155.4686584472656</v>
       </c>
       <c r="C93" t="n">
         <v>165.3699951171875</v>
@@ -3062,11 +3074,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B94" t="n">
-        <v>149.2435455322266</v>
+        <v>149.2435913085938</v>
       </c>
       <c r="C94" t="n">
         <v>158.5500030517578</v>
@@ -3091,11 +3103,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B95" t="n">
-        <v>150.9661407470703</v>
+        <v>150.9661254882812</v>
       </c>
       <c r="C95" t="n">
         <v>160.3800048828125</v>
@@ -3120,11 +3132,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B96" t="n">
-        <v>155.7855834960938</v>
+        <v>155.7855987548828</v>
       </c>
       <c r="C96" t="n">
         <v>165.5</v>
@@ -3149,11 +3161,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B97" t="n">
-        <v>145.4209594726562</v>
+        <v>145.4209747314453</v>
       </c>
       <c r="C97" t="n">
         <v>154.25</v>
@@ -3178,11 +3190,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B98" t="n">
-        <v>146.3543090820312</v>
+        <v>146.3543243408203</v>
       </c>
       <c r="C98" t="n">
         <v>155.2400054931641</v>
@@ -3207,11 +3219,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B99" t="n">
-        <v>148.4661102294922</v>
+        <v>148.4660491943359</v>
       </c>
       <c r="C99" t="n">
         <v>157.4799957275391</v>
@@ -3236,11 +3248,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B100" t="n">
-        <v>163.3690185546875</v>
+        <v>163.3689727783203</v>
       </c>
       <c r="C100" t="n">
         <v>173.0299987792969</v>
@@ -3265,11 +3277,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B101" t="n">
-        <v>166.8152008056641</v>
+        <v>166.815185546875</v>
       </c>
       <c r="C101" t="n">
         <v>176.6799926757812</v>
@@ -3294,11 +3306,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B102" t="n">
-        <v>175.9547576904297</v>
+        <v>175.9547271728516</v>
       </c>
       <c r="C102" t="n">
         <v>186.3600006103516</v>
@@ -3323,11 +3335,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B103" t="n">
-        <v>191.6245727539062</v>
+        <v>191.6245574951172</v>
       </c>
       <c r="C103" t="n">
         <v>202.6999969482422</v>
@@ -3352,11 +3364,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B104" t="n">
-        <v>193.3829345703125</v>
+        <v>193.3829498291016</v>
       </c>
       <c r="C104" t="n">
         <v>204.5599975585938</v>
@@ -3381,11 +3393,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B105" t="n">
-        <v>183.5322570800781</v>
+        <v>183.5323028564453</v>
       </c>
       <c r="C105" t="n">
         <v>194.1399993896484</v>
@@ -3410,11 +3422,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B106" t="n">
-        <v>204.6310729980469</v>
+        <v>204.6310424804688</v>
       </c>
       <c r="C106" t="n">
         <v>216.1999969482422</v>
@@ -3439,11 +3451,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B107" t="n">
-        <v>210.1585388183594</v>
+        <v>210.1585083007812</v>
       </c>
       <c r="C107" t="n">
         <v>222.0399932861328</v>
@@ -3468,11 +3480,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B108" t="n">
-        <v>230.9718322753906</v>
+        <v>230.9718627929688</v>
       </c>
       <c r="C108" t="n">
         <v>244.0299987792969</v>
@@ -3497,11 +3509,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B109" t="n">
-        <v>189.4027709960938</v>
+        <v>189.4028167724609</v>
       </c>
       <c r="C109" t="n">
         <v>199.7899932861328</v>
@@ -3526,11 +3538,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B110" t="n">
-        <v>183.5820465087891</v>
+        <v>183.58203125</v>
       </c>
       <c r="C110" t="n">
         <v>193.6499938964844</v>
@@ -3555,11 +3567,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B111" t="n">
-        <v>178.7851104736328</v>
+        <v>178.7851257324219</v>
       </c>
       <c r="C111" t="n">
         <v>188.5899963378906</v>
@@ -3584,7 +3596,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B112" t="n">
@@ -3613,11 +3625,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B113" t="n">
-        <v>162.3270111083984</v>
+        <v>162.3269805908203</v>
       </c>
       <c r="C113" t="n">
         <v>170.9299926757812</v>
@@ -3642,11 +3654,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B114" t="n">
-        <v>163.2386627197266</v>
+        <v>163.2386474609375</v>
       </c>
       <c r="C114" t="n">
         <v>171.8899993896484</v>
@@ -3671,11 +3683,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B115" t="n">
-        <v>173.6802978515625</v>
+        <v>173.6802825927734</v>
       </c>
       <c r="C115" t="n">
         <v>182.5500030517578</v>
@@ -3700,7 +3712,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B116" t="n">
@@ -3729,11 +3741,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B117" t="n">
-        <v>141.0848999023438</v>
+        <v>141.0849304199219</v>
       </c>
       <c r="C117" t="n">
         <v>148.2899932861328</v>
@@ -3758,11 +3770,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B118" t="n">
-        <v>143.7587585449219</v>
+        <v>143.7587738037109</v>
       </c>
       <c r="C118" t="n">
         <v>150.7799987792969</v>
@@ -3787,11 +3799,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B119" t="n">
-        <v>146.9623107910156</v>
+        <v>146.9622802734375</v>
       </c>
       <c r="C119" t="n">
         <v>154.1399993896484</v>
@@ -3816,7 +3828,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B120" t="n">
@@ -3845,11 +3857,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B121" t="n">
-        <v>158.1545257568359</v>
+        <v>158.1545104980469</v>
       </c>
       <c r="C121" t="n">
         <v>165.4900054931641</v>
@@ -3874,7 +3886,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B122" t="n">
@@ -3903,11 +3915,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B123" t="n">
-        <v>159.0623931884766</v>
+        <v>159.0624237060547</v>
       </c>
       <c r="C123" t="n">
         <v>166.4400024414062</v>
@@ -3932,11 +3944,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B124" t="n">
-        <v>168.3491821289062</v>
+        <v>168.3491668701172</v>
       </c>
       <c r="C124" t="n">
         <v>175.7799987792969</v>
@@ -3961,7 +3973,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B125" t="n">
@@ -3990,11 +4002,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B126" t="n">
-        <v>164.9300994873047</v>
+        <v>164.9301147460938</v>
       </c>
       <c r="C126" t="n">
         <v>172.2100067138672</v>
@@ -4019,11 +4031,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B127" t="n">
-        <v>180.5349731445312</v>
+        <v>180.5349578857422</v>
       </c>
       <c r="C127" t="n">
         <v>188.0899963378906</v>
@@ -4048,11 +4060,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B128" t="n">
-        <v>182.8577575683594</v>
+        <v>182.8577423095703</v>
       </c>
       <c r="C128" t="n">
         <v>190.5099945068359</v>
@@ -4077,11 +4089,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B129" t="n">
-        <v>166.9917144775391</v>
+        <v>166.9917449951172</v>
       </c>
       <c r="C129" t="n">
         <v>173.9799957275391</v>
@@ -4106,7 +4118,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B130" t="n">
@@ -4135,11 +4147,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B131" t="n">
-        <v>169.9796905517578</v>
+        <v>169.9796752929688</v>
       </c>
       <c r="C131" t="n">
         <v>176.6699981689453</v>
@@ -4164,11 +4176,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B132" t="n">
-        <v>189.8957824707031</v>
+        <v>189.8957672119141</v>
       </c>
       <c r="C132" t="n">
         <v>197.3699951171875</v>
@@ -4193,7 +4205,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B133" t="n">
@@ -4222,7 +4234,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B134" t="n">
@@ -4251,7 +4263,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B135" t="n">
@@ -4280,11 +4292,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B136" t="n">
-        <v>153.9950408935547</v>
+        <v>153.9950561523438</v>
       </c>
       <c r="C136" t="n">
         <v>159.2400054931641</v>
@@ -4309,11 +4321,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B137" t="n">
-        <v>163.9751434326172</v>
+        <v>163.9751586914062</v>
       </c>
       <c r="C137" t="n">
         <v>169.5599975585938</v>
@@ -4338,11 +4350,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B138" t="n">
-        <v>167.6499938964844</v>
+        <v>167.6499786376953</v>
       </c>
       <c r="C138" t="n">
         <v>173.3600006103516</v>
@@ -4367,7 +4379,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B139" t="n">
@@ -4396,11 +4408,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B140" t="n">
-        <v>177.868408203125</v>
+        <v>177.8684234619141</v>
       </c>
       <c r="C140" t="n">
         <v>183.4900054931641</v>
@@ -4425,11 +4437,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B141" t="n">
-        <v>189.3941192626953</v>
+        <v>189.3941497802734</v>
       </c>
       <c r="C141" t="n">
         <v>195.3800048828125</v>
@@ -4454,11 +4466,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B142" t="n">
-        <v>173.7133636474609</v>
+        <v>173.71337890625</v>
       </c>
       <c r="C142" t="n">
         <v>178.7799987792969</v>
@@ -4483,11 +4495,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B143" t="n">
-        <v>170.283447265625</v>
+        <v>170.2834014892578</v>
       </c>
       <c r="C143" t="n">
         <v>175.25</v>
@@ -4512,11 +4524,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B144" t="n">
-        <v>158.3125457763672</v>
+        <v>158.3125610351562</v>
       </c>
       <c r="C144" t="n">
         <v>162.9299926757812</v>
@@ -4541,11 +4553,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B145" t="n">
-        <v>166.5587005615234</v>
+        <v>166.5587158203125</v>
       </c>
       <c r="C145" t="n">
         <v>170.8999938964844</v>
@@ -4570,11 +4582,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B146" t="n">
-        <v>162.99169921875</v>
+        <v>162.9916839599609</v>
       </c>
       <c r="C146" t="n">
         <v>167.2400054931641</v>
@@ -4599,7 +4611,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B147" t="n">
@@ -4628,7 +4640,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B148" t="n">
@@ -4657,11 +4669,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B149" t="n">
-        <v>164.9009552001953</v>
+        <v>164.9009399414062</v>
       </c>
       <c r="C149" t="n">
         <v>168.6300048828125</v>
@@ -4686,7 +4698,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B150" t="n">
@@ -4715,7 +4727,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B151" t="n">
@@ -4744,7 +4756,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B152" t="n">
@@ -4773,7 +4785,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B153" t="n">
@@ -4802,7 +4814,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B154" t="n">
@@ -4831,7 +4843,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B155" t="n">
@@ -4860,11 +4872,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B156" t="n">
-        <v>123.8788909912109</v>
+        <v>123.8788986206055</v>
       </c>
       <c r="C156" t="n">
         <v>125.8199996948242</v>
@@ -4889,7 +4901,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B157" t="n">
@@ -4918,7 +4930,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B158" t="n">
@@ -4947,7 +4959,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B159" t="n">
@@ -4976,7 +4988,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B160" t="n">
@@ -5005,7 +5017,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B161" t="n">
@@ -5034,7 +5046,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B162" t="n">
@@ -5063,7 +5075,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B163" t="n">
@@ -5092,7 +5104,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B164" t="n">
@@ -5121,32 +5133,32 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B165" t="n">
-        <v>71.61000061035156</v>
+        <v>70.26999664306641</v>
       </c>
       <c r="C165" t="n">
-        <v>71.61000061035156</v>
+        <v>70.26999664306641</v>
       </c>
       <c r="D165" t="n">
-        <v>75490600</v>
+        <v>78860000</v>
       </c>
       <c r="E165" t="n">
         <v>6.069999999999999</v>
       </c>
       <c r="F165" t="n">
-        <v>11.79736418621937</v>
+        <v>11.57660570725971</v>
       </c>
       <c r="G165" t="n">
         <v>413223602</v>
       </c>
       <c r="H165" t="n">
-        <v>29590942391.43167</v>
+        <v>29037221125.37581</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1826870479677974</v>
+        <v>0.1908409868611522</v>
       </c>
     </row>
   </sheetData>
@@ -5178,75 +5190,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>41409</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -5282,13 +5294,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>41001</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>41500</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -5324,13 +5336,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>41092</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>41591</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -5366,13 +5378,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>41724</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -5399,7 +5411,7 @@
       <c r="I5" t="n">
         <v>0.87</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>41724</v>
       </c>
       <c r="K5" t="n">
@@ -5412,13 +5424,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>41409</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -5445,7 +5457,7 @@
       <c r="I6" t="n">
         <v>0.9299999999999999</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>41724</v>
       </c>
       <c r="K6" t="n">
@@ -5458,13 +5470,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>41500</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -5491,7 +5503,7 @@
       <c r="I7" t="n">
         <v>0.8400000000000001</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>41724</v>
       </c>
       <c r="K7" t="n">
@@ -5504,13 +5516,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41546</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>41591</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -5537,7 +5549,7 @@
       <c r="I8" t="n">
         <v>0.78</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>41724</v>
       </c>
       <c r="K8" t="n">
@@ -5550,13 +5562,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>41724</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -5583,7 +5595,7 @@
       <c r="I9" t="n">
         <v>1.01</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>41724</v>
       </c>
       <c r="K9" t="n">
@@ -5596,13 +5608,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41728</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>41772</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -5629,7 +5641,7 @@
       <c r="I10" t="n">
         <v>1.04</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>41772</v>
       </c>
       <c r="K10" t="n">
@@ -5642,13 +5654,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41819</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>41863</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -5675,7 +5687,7 @@
       <c r="I11" t="n">
         <v>1.05</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>41863</v>
       </c>
       <c r="K11" t="n">
@@ -5688,13 +5700,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41910</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>41953</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -5721,7 +5733,7 @@
       <c r="I12" t="n">
         <v>1.12</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>41953</v>
       </c>
       <c r="K12" t="n">
@@ -5734,13 +5746,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41911</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -5767,7 +5779,7 @@
       <c r="I13" t="n">
         <v>1.16</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="K13" t="n">
@@ -5780,13 +5792,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>42092</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -5813,7 +5825,7 @@
       <c r="I14" t="n">
         <v>1.18</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="K14" t="n">
@@ -5826,13 +5838,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42093</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>42183</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -5859,7 +5871,7 @@
       <c r="I15" t="n">
         <v>0.8400000000000001</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="K15" t="n">
@@ -5872,13 +5884,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42184</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>42274</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -5905,7 +5917,7 @@
       <c r="I16" t="n">
         <v>0.8899999999999999</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="K16" t="n">
@@ -5918,13 +5930,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42275</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -5951,7 +5963,7 @@
       <c r="I17" t="n">
         <v>0.6799999999999999</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="K17" t="n">
@@ -5964,13 +5976,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>42463</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -5997,7 +6009,7 @@
       <c r="I18" t="n">
         <v>0.76</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="K18" t="n">
@@ -6010,13 +6022,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>42464</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>42554</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -6043,7 +6055,7 @@
       <c r="I19" t="n">
         <v>1.28</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="K19" t="n">
@@ -6056,13 +6068,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42555</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42645</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -6089,7 +6101,7 @@
       <c r="I20" t="n">
         <v>1.38</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="K20" t="n">
@@ -6102,13 +6114,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42646</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>42782</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -6135,7 +6147,7 @@
       <c r="I21" t="n">
         <v>1.65</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>42782</v>
       </c>
       <c r="K21" t="n">
@@ -6148,13 +6160,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42827</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -6181,7 +6193,7 @@
       <c r="I22" t="n">
         <v>1.72</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="K22" t="n">
@@ -6194,13 +6206,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42828</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42918</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>42955</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -6227,7 +6239,7 @@
       <c r="I23" t="n">
         <v>1.77</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>42955</v>
       </c>
       <c r="K23" t="n">
@@ -6240,13 +6252,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42919</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -6273,7 +6285,7 @@
       <c r="I24" t="n">
         <v>1.9</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="K24" t="n">
@@ -6286,13 +6298,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>43010</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -6319,7 +6331,7 @@
       <c r="I25" t="n">
         <v>1.75</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="K25" t="n">
@@ -6332,13 +6344,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -6365,7 +6377,7 @@
       <c r="I26" t="n">
         <v>1.99</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="K26" t="n">
@@ -6378,13 +6390,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -6411,7 +6423,7 @@
       <c r="I27" t="n">
         <v>2.28</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="K27" t="n">
@@ -6424,13 +6436,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -6457,7 +6469,7 @@
       <c r="I28" t="n">
         <v>2.38</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="K28" t="n">
@@ -6470,13 +6482,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>43510</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -6503,7 +6515,7 @@
       <c r="I29" t="n">
         <v>2.93</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>43510</v>
       </c>
       <c r="K29" t="n">
@@ -6516,13 +6528,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -6549,7 +6561,7 @@
       <c r="I30" t="n">
         <v>2.86</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="K30" t="n">
@@ -6562,13 +6574,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -6595,7 +6607,7 @@
       <c r="I31" t="n">
         <v>2.84</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="K31" t="n">
@@ -6608,13 +6620,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>43776</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -6641,7 +6653,7 @@
       <c r="I32" t="n">
         <v>3.03</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>43776</v>
       </c>
       <c r="K32" t="n">
@@ -6654,13 +6666,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -6687,7 +6699,7 @@
       <c r="I33" t="n">
         <v>3.12</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="K33" t="n">
@@ -6700,13 +6712,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -6733,7 +6745,7 @@
       <c r="I34" t="n">
         <v>3.35</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="K34" t="n">
@@ -6746,13 +6758,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -6779,7 +6791,7 @@
       <c r="I35" t="n">
         <v>3.37</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="K35" t="n">
@@ -6792,13 +6804,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -6825,7 +6837,7 @@
       <c r="I36" t="n">
         <v>3.47</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="K36" t="n">
@@ -6838,13 +6850,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>44243</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -6871,7 +6883,7 @@
       <c r="I37" t="n">
         <v>3.42</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>44243</v>
       </c>
       <c r="K37" t="n">
@@ -6884,13 +6896,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -6917,7 +6929,7 @@
       <c r="I38" t="n">
         <v>3.71</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="K38" t="n">
@@ -6930,13 +6942,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -6963,7 +6975,7 @@
       <c r="I39" t="n">
         <v>3.99</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="K39" t="n">
@@ -6976,13 +6988,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -7009,7 +7021,7 @@
       <c r="I40" t="n">
         <v>4.15</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="K40" t="n">
@@ -7022,13 +7034,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>44607</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -7055,7 +7067,7 @@
       <c r="I41" t="n">
         <v>4.27</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>44607</v>
       </c>
       <c r="K41" t="n">
@@ -7068,13 +7080,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -7101,7 +7113,7 @@
       <c r="I42" t="n">
         <v>4.359999999999999</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="K42" t="n">
@@ -7114,13 +7126,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -7147,7 +7159,7 @@
       <c r="I43" t="n">
         <v>4.409999999999999</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="K43" t="n">
@@ -7160,13 +7172,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -7193,7 +7205,7 @@
       <c r="I44" t="n">
         <v>4.379999999999999</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="K44" t="n">
@@ -7206,13 +7218,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -7239,7 +7251,7 @@
       <c r="I45" t="n">
         <v>4.49</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="K45" t="n">
@@ -7252,13 +7264,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -7285,7 +7297,7 @@
       <c r="I46" t="n">
         <v>4.42</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="K46" t="n">
@@ -7298,13 +7310,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>45146</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -7331,7 +7343,7 @@
       <c r="I47" t="n">
         <v>4.75</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>45146</v>
       </c>
       <c r="K47" t="n">
@@ -7344,13 +7356,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -7377,7 +7389,7 @@
       <c r="I48" t="n">
         <v>4.91</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K48" t="n">
@@ -7390,13 +7402,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>45335</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -7423,7 +7435,7 @@
       <c r="I49" t="n">
         <v>5.07</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>45335</v>
       </c>
       <c r="K49" t="n">
@@ -7436,13 +7448,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -7469,7 +7481,7 @@
       <c r="I50" t="n">
         <v>5.19</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K50" t="n">
@@ -7482,13 +7494,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -7515,7 +7527,7 @@
       <c r="I51" t="n">
         <v>5.11</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="K51" t="n">
@@ -7528,13 +7540,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -7561,7 +7573,7 @@
       <c r="I52" t="n">
         <v>5.32</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="K52" t="n">
@@ -7574,13 +7586,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -7607,7 +7619,7 @@
       <c r="I53" t="n">
         <v>5.47</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="K53" t="n">
@@ -7620,13 +7632,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -7653,7 +7665,7 @@
       <c r="I54" t="n">
         <v>5.57</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="K54" t="n">
@@ -7666,13 +7678,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -7699,7 +7711,7 @@
       <c r="I55" t="n">
         <v>5.81</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="K55" t="n">
@@ -7712,13 +7724,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -7745,7 +7757,7 @@
       <c r="I56" t="n">
         <v>5.94</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="K56" t="n">
@@ -7758,13 +7770,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -7791,7 +7803,7 @@
       <c r="I57" t="n">
         <v>6.02</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="K57" t="n">
@@ -7804,13 +7816,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -7837,7 +7849,7 @@
       <c r="I58" t="n">
         <v>6.029999999999999</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="K58" t="n">
@@ -7850,13 +7862,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -7883,7 +7895,7 @@
       <c r="I59" t="n">
         <v>6.069999999999999</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="K59" t="n">
@@ -7920,52 +7932,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>41495</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>41500</v>
       </c>
       <c r="C2" t="n">
@@ -7994,10 +8006,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>41586</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>41591</v>
       </c>
       <c r="C3" t="n">
@@ -8026,10 +8038,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>41717</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>41724</v>
       </c>
       <c r="C4" t="n">
@@ -8058,10 +8070,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>41768</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>41772</v>
       </c>
       <c r="C5" t="n">
@@ -8090,10 +8102,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>41859</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>41863</v>
       </c>
       <c r="C6" t="n">
@@ -8122,10 +8134,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>41950</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>41953</v>
       </c>
       <c r="C7" t="n">
@@ -8154,10 +8166,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42058</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>42062</v>
       </c>
       <c r="C8" t="n">
@@ -8186,10 +8198,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42125</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="C9" t="n">
@@ -8218,10 +8230,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42219</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>42222</v>
       </c>
       <c r="C10" t="n">
@@ -8250,10 +8262,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42310</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>42313</v>
       </c>
       <c r="C11" t="n">
@@ -8282,10 +8294,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42419</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="C12" t="n">
@@ -8314,10 +8326,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42489</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>42496</v>
       </c>
       <c r="C13" t="n">
@@ -8346,10 +8358,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42583</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>42587</v>
       </c>
       <c r="C14" t="n">
@@ -8378,10 +8390,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>42677</v>
       </c>
       <c r="C15" t="n">
@@ -8410,10 +8422,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>42776</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>42782</v>
       </c>
       <c r="C16" t="n">
@@ -8442,10 +8454,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>42853</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="C17" t="n">
@@ -8474,10 +8486,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>42949</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>42955</v>
       </c>
       <c r="C18" t="n">
@@ -8506,10 +8518,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>43034</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>43041</v>
       </c>
       <c r="C19" t="n">
@@ -8538,10 +8550,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>43140</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>43146</v>
       </c>
       <c r="C20" t="n">
@@ -8570,10 +8582,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>43217</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>43222</v>
       </c>
       <c r="C21" t="n">
@@ -8602,10 +8614,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>43308</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="C22" t="n">
@@ -8634,10 +8646,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>43399</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>43405</v>
       </c>
       <c r="C23" t="n">
@@ -8666,10 +8678,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>43504</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>43510</v>
       </c>
       <c r="C24" t="n">
@@ -8698,10 +8710,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>43581</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>43587</v>
       </c>
       <c r="C25" t="n">
@@ -8730,10 +8742,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43679</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>43686</v>
       </c>
       <c r="C26" t="n">
@@ -8762,10 +8774,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43770</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43776</v>
       </c>
       <c r="C27" t="n">
@@ -8794,10 +8806,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43868</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43874</v>
       </c>
       <c r="C28" t="n">
@@ -8826,10 +8838,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43952</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43957</v>
       </c>
       <c r="C29" t="n">
@@ -8858,10 +8870,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="C30" t="n">
@@ -8890,10 +8902,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>44134</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="C31" t="n">
@@ -8922,10 +8934,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44238</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>44243</v>
       </c>
       <c r="C32" t="n">
@@ -8954,10 +8966,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="C33" t="n">
@@ -8986,10 +8998,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44407</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="C34" t="n">
@@ -9018,10 +9030,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44498</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="C35" t="n">
@@ -9050,10 +9062,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44603</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>44607</v>
       </c>
       <c r="C36" t="n">
@@ -9082,10 +9094,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44680</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>44686</v>
       </c>
       <c r="C37" t="n">
@@ -9114,10 +9126,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44771</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44777</v>
       </c>
       <c r="C38" t="n">
@@ -9146,10 +9158,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44862</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="C39" t="n">
@@ -9178,10 +9190,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44967</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44971</v>
       </c>
       <c r="C40" t="n">
@@ -9210,10 +9222,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>45044</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="C41" t="n">
@@ -9242,10 +9254,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>45142</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>45146</v>
       </c>
       <c r="C42" t="n">
@@ -9274,10 +9286,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45226</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C43" t="n">
@@ -9306,10 +9318,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45331</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>45335</v>
       </c>
       <c r="C44" t="n">
@@ -9338,10 +9350,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45408</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C45" t="n">
@@ -9370,10 +9382,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45506</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>45510</v>
       </c>
       <c r="C46" t="n">
@@ -9402,10 +9414,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>45600</v>
       </c>
       <c r="C47" t="n">
@@ -9434,10 +9446,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45695</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>45701</v>
       </c>
       <c r="C48" t="n">
@@ -9466,10 +9478,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45779</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>45783</v>
       </c>
       <c r="C49" t="n">
@@ -9498,10 +9510,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45874</v>
       </c>
       <c r="C50" t="n">
@@ -9530,10 +9542,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45965</v>
       </c>
       <c r="C51" t="n">
@@ -9562,10 +9574,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>46059</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="C52" t="n">
@@ -9594,10 +9606,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="C53" t="n">
@@ -9626,10 +9638,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>46240</v>
       </c>
       <c r="C54" t="n">
@@ -9676,12 +9688,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/ZTS.xlsx
+++ b/salidas/empresas/ZTS.xlsx
@@ -498,7 +498,7 @@
         <v>41333</v>
       </c>
       <c r="B2" t="n">
-        <v>29.77680206298828</v>
+        <v>29.77681732177734</v>
       </c>
       <c r="C2" t="n">
         <v>33.45000076293945</v>
@@ -517,7 +517,7 @@
         <v>41364</v>
       </c>
       <c r="B3" t="n">
-        <v>29.73230934143066</v>
+        <v>29.7323055267334</v>
       </c>
       <c r="C3" t="n">
         <v>33.40000152587891</v>
@@ -536,7 +536,7 @@
         <v>41394</v>
       </c>
       <c r="B4" t="n">
-        <v>29.45268440246582</v>
+        <v>29.45267868041992</v>
       </c>
       <c r="C4" t="n">
         <v>33.02000045776367</v>
@@ -555,7 +555,7 @@
         <v>41425</v>
       </c>
       <c r="B5" t="n">
-        <v>28.54287528991699</v>
+        <v>28.54287719726562</v>
       </c>
       <c r="C5" t="n">
         <v>32</v>
@@ -574,7 +574,7 @@
         <v>41455</v>
       </c>
       <c r="B6" t="n">
-        <v>27.55279922485352</v>
+        <v>27.55278968811035</v>
       </c>
       <c r="C6" t="n">
         <v>30.88999938964844</v>
@@ -593,7 +593,7 @@
         <v>41486</v>
       </c>
       <c r="B7" t="n">
-        <v>26.64703178405762</v>
+        <v>26.64703369140625</v>
       </c>
       <c r="C7" t="n">
         <v>29.80999946594238</v>
@@ -612,7 +612,7 @@
         <v>41517</v>
       </c>
       <c r="B8" t="n">
-        <v>26.05705070495605</v>
+        <v>26.05706024169922</v>
       </c>
       <c r="C8" t="n">
         <v>29.14999961853027</v>
@@ -637,7 +637,7 @@
         <v>41547</v>
       </c>
       <c r="B9" t="n">
-        <v>27.81802940368652</v>
+        <v>27.81803703308105</v>
       </c>
       <c r="C9" t="n">
         <v>31.1200008392334</v>
@@ -662,7 +662,7 @@
         <v>41578</v>
       </c>
       <c r="B10" t="n">
-        <v>28.35828971862793</v>
+        <v>28.35829734802246</v>
       </c>
       <c r="C10" t="n">
         <v>31.65999984741211</v>
@@ -687,7 +687,7 @@
         <v>41608</v>
       </c>
       <c r="B11" t="n">
-        <v>27.90147399902344</v>
+        <v>27.90146636962891</v>
       </c>
       <c r="C11" t="n">
         <v>31.14999961853027</v>
@@ -712,7 +712,7 @@
         <v>41639</v>
       </c>
       <c r="B12" t="n">
-        <v>29.28086471557617</v>
+        <v>29.2808780670166</v>
       </c>
       <c r="C12" t="n">
         <v>32.68999862670898</v>
@@ -737,7 +737,7 @@
         <v>41670</v>
       </c>
       <c r="B13" t="n">
-        <v>27.25643730163574</v>
+        <v>27.25643920898438</v>
       </c>
       <c r="C13" t="n">
         <v>30.36000061035156</v>
@@ -762,7 +762,7 @@
         <v>41698</v>
       </c>
       <c r="B14" t="n">
-        <v>27.8489818572998</v>
+        <v>27.84897613525391</v>
       </c>
       <c r="C14" t="n">
         <v>31.02000045776367</v>
@@ -787,7 +787,7 @@
         <v>41729</v>
       </c>
       <c r="B15" t="n">
-        <v>25.98159408569336</v>
+        <v>25.98161125183105</v>
       </c>
       <c r="C15" t="n">
         <v>28.94000053405762</v>
@@ -845,7 +845,7 @@
         <v>41790</v>
       </c>
       <c r="B17" t="n">
-        <v>27.62937355041504</v>
+        <v>27.62936973571777</v>
       </c>
       <c r="C17" t="n">
         <v>30.70000076293945</v>
@@ -874,7 +874,7 @@
         <v>41820</v>
       </c>
       <c r="B18" t="n">
-        <v>29.04233741760254</v>
+        <v>29.04234504699707</v>
       </c>
       <c r="C18" t="n">
         <v>32.27000045776367</v>
@@ -903,7 +903,7 @@
         <v>41851</v>
       </c>
       <c r="B19" t="n">
-        <v>29.61833000183105</v>
+        <v>29.61833190917969</v>
       </c>
       <c r="C19" t="n">
         <v>32.90999984741211</v>
@@ -932,7 +932,7 @@
         <v>41882</v>
       </c>
       <c r="B20" t="n">
-        <v>31.96357917785645</v>
+        <v>31.96357345581055</v>
       </c>
       <c r="C20" t="n">
         <v>35.43999862670898</v>
@@ -961,7 +961,7 @@
         <v>41912</v>
       </c>
       <c r="B21" t="n">
-        <v>33.32546234130859</v>
+        <v>33.32546997070312</v>
       </c>
       <c r="C21" t="n">
         <v>36.95000076293945</v>
@@ -990,7 +990,7 @@
         <v>41943</v>
       </c>
       <c r="B22" t="n">
-        <v>33.51486968994141</v>
+        <v>33.51486206054688</v>
       </c>
       <c r="C22" t="n">
         <v>37.15999984741211</v>
@@ -1019,7 +1019,7 @@
         <v>41973</v>
       </c>
       <c r="B23" t="n">
-        <v>40.60134506225586</v>
+        <v>40.60133743286133</v>
       </c>
       <c r="C23" t="n">
         <v>44.93000030517578</v>
@@ -1048,7 +1048,7 @@
         <v>42004</v>
       </c>
       <c r="B24" t="n">
-        <v>38.88440322875977</v>
+        <v>38.8843879699707</v>
       </c>
       <c r="C24" t="n">
         <v>43.02999877929688</v>
@@ -1077,7 +1077,7 @@
         <v>42035</v>
       </c>
       <c r="B25" t="n">
-        <v>38.6859245300293</v>
+        <v>38.68589782714844</v>
       </c>
       <c r="C25" t="n">
         <v>42.72999954223633</v>
@@ -1106,7 +1106,7 @@
         <v>42063</v>
       </c>
       <c r="B26" t="n">
-        <v>41.72791290283203</v>
+        <v>41.72790908813477</v>
       </c>
       <c r="C26" t="n">
         <v>46.09000015258789</v>
@@ -1135,7 +1135,7 @@
         <v>42094</v>
       </c>
       <c r="B27" t="n">
-        <v>41.90898513793945</v>
+        <v>41.90899658203125</v>
       </c>
       <c r="C27" t="n">
         <v>46.29000091552734</v>
@@ -1164,7 +1164,7 @@
         <v>42124</v>
       </c>
       <c r="B28" t="n">
-        <v>40.28813934326172</v>
+        <v>40.28813552856445</v>
       </c>
       <c r="C28" t="n">
         <v>44.41999816894531</v>
@@ -1193,7 +1193,7 @@
         <v>42155</v>
       </c>
       <c r="B29" t="n">
-        <v>45.14049911499023</v>
+        <v>45.1404914855957</v>
       </c>
       <c r="C29" t="n">
         <v>49.77000045776367</v>
@@ -1222,7 +1222,7 @@
         <v>42185</v>
       </c>
       <c r="B30" t="n">
-        <v>43.73467254638672</v>
+        <v>43.73468017578125</v>
       </c>
       <c r="C30" t="n">
         <v>48.22000122070312</v>
@@ -1251,7 +1251,7 @@
         <v>42216</v>
       </c>
       <c r="B31" t="n">
-        <v>44.42397308349609</v>
+        <v>44.42398834228516</v>
       </c>
       <c r="C31" t="n">
         <v>48.97999954223633</v>
@@ -1280,7 +1280,7 @@
         <v>42247</v>
       </c>
       <c r="B32" t="n">
-        <v>40.76620864868164</v>
+        <v>40.76620483398438</v>
       </c>
       <c r="C32" t="n">
         <v>44.86999893188477</v>
@@ -1309,7 +1309,7 @@
         <v>42277</v>
       </c>
       <c r="B33" t="n">
-        <v>37.4136962890625</v>
+        <v>37.41369247436523</v>
       </c>
       <c r="C33" t="n">
         <v>41.18000030517578</v>
@@ -1338,7 +1338,7 @@
         <v>42308</v>
       </c>
       <c r="B34" t="n">
-        <v>39.07632064819336</v>
+        <v>39.07631683349609</v>
       </c>
       <c r="C34" t="n">
         <v>43.0099983215332</v>
@@ -1367,7 +1367,7 @@
         <v>42338</v>
       </c>
       <c r="B35" t="n">
-        <v>42.50857162475586</v>
+        <v>42.50858306884766</v>
       </c>
       <c r="C35" t="n">
         <v>46.70000076293945</v>
@@ -1396,7 +1396,7 @@
         <v>42369</v>
       </c>
       <c r="B36" t="n">
-        <v>43.61908721923828</v>
+        <v>43.61909484863281</v>
       </c>
       <c r="C36" t="n">
         <v>47.91999816894531</v>
@@ -1425,7 +1425,7 @@
         <v>42400</v>
       </c>
       <c r="B37" t="n">
-        <v>39.27219009399414</v>
+        <v>39.27217864990234</v>
       </c>
       <c r="C37" t="n">
         <v>43.04999923706055</v>
@@ -1454,7 +1454,7 @@
         <v>42429</v>
       </c>
       <c r="B38" t="n">
-        <v>37.45680999755859</v>
+        <v>37.45681381225586</v>
       </c>
       <c r="C38" t="n">
         <v>41.06000137329102</v>
@@ -1483,7 +1483,7 @@
         <v>42460</v>
       </c>
       <c r="B39" t="n">
-        <v>40.43986511230469</v>
+        <v>40.43986129760742</v>
       </c>
       <c r="C39" t="n">
         <v>44.33000183105469</v>
@@ -1512,7 +1512,7 @@
         <v>42490</v>
       </c>
       <c r="B40" t="n">
-        <v>42.9921875</v>
+        <v>42.99219512939453</v>
       </c>
       <c r="C40" t="n">
         <v>47.02999877929688</v>
@@ -1541,7 +1541,7 @@
         <v>42521</v>
       </c>
       <c r="B41" t="n">
-        <v>43.34870529174805</v>
+        <v>43.34868621826172</v>
       </c>
       <c r="C41" t="n">
         <v>47.41999816894531</v>
@@ -1570,7 +1570,7 @@
         <v>42551</v>
       </c>
       <c r="B42" t="n">
-        <v>43.4761962890625</v>
+        <v>43.47619247436523</v>
       </c>
       <c r="C42" t="n">
         <v>47.45999908447266</v>
@@ -1628,7 +1628,7 @@
         <v>42613</v>
       </c>
       <c r="B44" t="n">
-        <v>46.81064605712891</v>
+        <v>46.81065368652344</v>
       </c>
       <c r="C44" t="n">
         <v>51.09999847412109</v>
@@ -1657,7 +1657,7 @@
         <v>42643</v>
       </c>
       <c r="B45" t="n">
-        <v>47.64426040649414</v>
+        <v>47.64426803588867</v>
       </c>
       <c r="C45" t="n">
         <v>52.0099983215332</v>
@@ -1686,7 +1686,7 @@
         <v>42674</v>
       </c>
       <c r="B46" t="n">
-        <v>43.78765106201172</v>
+        <v>43.78765487670898</v>
       </c>
       <c r="C46" t="n">
         <v>47.79999923706055</v>
@@ -1715,7 +1715,7 @@
         <v>42704</v>
       </c>
       <c r="B47" t="n">
-        <v>46.24300765991211</v>
+        <v>46.24298477172852</v>
       </c>
       <c r="C47" t="n">
         <v>50.38000106811523</v>
@@ -1744,7 +1744,7 @@
         <v>42735</v>
       </c>
       <c r="B48" t="n">
-        <v>49.13433456420898</v>
+        <v>49.13433837890625</v>
       </c>
       <c r="C48" t="n">
         <v>53.52999877929688</v>
@@ -1773,7 +1773,7 @@
         <v>42766</v>
       </c>
       <c r="B49" t="n">
-        <v>50.52823257446289</v>
+        <v>50.52821731567383</v>
       </c>
       <c r="C49" t="n">
         <v>54.93999862670898</v>
@@ -1802,7 +1802,7 @@
         <v>42794</v>
       </c>
       <c r="B50" t="n">
-        <v>49.02912521362305</v>
+        <v>49.02911758422852</v>
       </c>
       <c r="C50" t="n">
         <v>53.31000137329102</v>
@@ -1831,7 +1831,7 @@
         <v>42825</v>
       </c>
       <c r="B51" t="n">
-        <v>49.08430099487305</v>
+        <v>49.08430862426758</v>
       </c>
       <c r="C51" t="n">
         <v>53.36999893188477</v>
@@ -1860,7 +1860,7 @@
         <v>42855</v>
       </c>
       <c r="B52" t="n">
-        <v>51.70639038085938</v>
+        <v>51.70638275146484</v>
       </c>
       <c r="C52" t="n">
         <v>56.11000061035156</v>
@@ -1889,7 +1889,7 @@
         <v>42886</v>
       </c>
       <c r="B53" t="n">
-        <v>57.39215469360352</v>
+        <v>57.39213943481445</v>
       </c>
       <c r="C53" t="n">
         <v>62.27999877929688</v>
@@ -1918,7 +1918,7 @@
         <v>42916</v>
       </c>
       <c r="B54" t="n">
-        <v>57.58206176757812</v>
+        <v>57.58206939697266</v>
       </c>
       <c r="C54" t="n">
         <v>62.38000106811523</v>
@@ -1947,7 +1947,7 @@
         <v>42947</v>
       </c>
       <c r="B55" t="n">
-        <v>57.7112922668457</v>
+        <v>57.71129608154297</v>
       </c>
       <c r="C55" t="n">
         <v>62.52000045776367</v>
@@ -2034,7 +2034,7 @@
         <v>43039</v>
       </c>
       <c r="B58" t="n">
-        <v>58.91130828857422</v>
+        <v>58.91131591796875</v>
       </c>
       <c r="C58" t="n">
         <v>63.81999969482422</v>
@@ -2063,7 +2063,7 @@
         <v>43069</v>
       </c>
       <c r="B59" t="n">
-        <v>66.83235931396484</v>
+        <v>66.83237457275391</v>
       </c>
       <c r="C59" t="n">
         <v>72.29000091552734</v>
@@ -2092,7 +2092,7 @@
         <v>43100</v>
       </c>
       <c r="B60" t="n">
-        <v>66.60121154785156</v>
+        <v>66.60125732421875</v>
       </c>
       <c r="C60" t="n">
         <v>72.04000091552734</v>
@@ -2121,7 +2121,7 @@
         <v>43131</v>
       </c>
       <c r="B61" t="n">
-        <v>71.05377197265625</v>
+        <v>71.05378723144531</v>
       </c>
       <c r="C61" t="n">
         <v>76.73000335693359</v>
@@ -2150,7 +2150,7 @@
         <v>43159</v>
       </c>
       <c r="B62" t="n">
-        <v>74.87824249267578</v>
+        <v>74.87822723388672</v>
       </c>
       <c r="C62" t="n">
         <v>80.86000061035156</v>
@@ -2208,7 +2208,7 @@
         <v>43220</v>
       </c>
       <c r="B64" t="n">
-        <v>77.41789245605469</v>
+        <v>77.41790771484375</v>
       </c>
       <c r="C64" t="n">
         <v>83.48000335693359</v>
@@ -2237,7 +2237,7 @@
         <v>43251</v>
       </c>
       <c r="B65" t="n">
-        <v>77.62193298339844</v>
+        <v>77.62191009521484</v>
       </c>
       <c r="C65" t="n">
         <v>83.69999694824219</v>
@@ -2266,7 +2266,7 @@
         <v>43281</v>
       </c>
       <c r="B66" t="n">
-        <v>79.00372314453125</v>
+        <v>79.00373077392578</v>
       </c>
       <c r="C66" t="n">
         <v>85.19000244140625</v>
@@ -2324,7 +2324,7 @@
         <v>43343</v>
       </c>
       <c r="B68" t="n">
-        <v>84.14420318603516</v>
+        <v>84.14423370361328</v>
       </c>
       <c r="C68" t="n">
         <v>90.59999847412109</v>
@@ -2353,7 +2353,7 @@
         <v>43373</v>
       </c>
       <c r="B69" t="n">
-        <v>85.03581237792969</v>
+        <v>85.03580474853516</v>
       </c>
       <c r="C69" t="n">
         <v>91.55999755859375</v>
@@ -2382,7 +2382,7 @@
         <v>43404</v>
       </c>
       <c r="B70" t="n">
-        <v>83.72628784179688</v>
+        <v>83.72628021240234</v>
       </c>
       <c r="C70" t="n">
         <v>90.15000152587891</v>
@@ -2411,7 +2411,7 @@
         <v>43434</v>
       </c>
       <c r="B71" t="n">
-        <v>87.30043029785156</v>
+        <v>87.3004150390625</v>
       </c>
       <c r="C71" t="n">
         <v>93.87000274658203</v>
@@ -2440,7 +2440,7 @@
         <v>43465</v>
       </c>
       <c r="B72" t="n">
-        <v>79.55341339111328</v>
+        <v>79.55339813232422</v>
       </c>
       <c r="C72" t="n">
         <v>85.54000091552734</v>
@@ -2469,7 +2469,7 @@
         <v>43496</v>
       </c>
       <c r="B73" t="n">
-        <v>80.28826141357422</v>
+        <v>80.28826904296875</v>
       </c>
       <c r="C73" t="n">
         <v>86.16000366210938</v>
@@ -2556,7 +2556,7 @@
         <v>43585</v>
       </c>
       <c r="B76" t="n">
-        <v>95.05686187744141</v>
+        <v>95.056884765625</v>
       </c>
       <c r="C76" t="n">
         <v>101.8399963378906</v>
@@ -2585,7 +2585,7 @@
         <v>43616</v>
       </c>
       <c r="B77" t="n">
-        <v>94.31951141357422</v>
+        <v>94.31949615478516</v>
       </c>
       <c r="C77" t="n">
         <v>101.0500030517578</v>
@@ -2643,7 +2643,7 @@
         <v>43677</v>
       </c>
       <c r="B79" t="n">
-        <v>107.3925857543945</v>
+        <v>107.3926162719727</v>
       </c>
       <c r="C79" t="n">
         <v>114.8899993896484</v>
@@ -2701,7 +2701,7 @@
         <v>43738</v>
       </c>
       <c r="B81" t="n">
-        <v>116.459587097168</v>
+        <v>116.4596176147461</v>
       </c>
       <c r="C81" t="n">
         <v>124.5899963378906</v>
@@ -2730,7 +2730,7 @@
         <v>43769</v>
       </c>
       <c r="B82" t="n">
-        <v>119.7255554199219</v>
+        <v>119.7255401611328</v>
       </c>
       <c r="C82" t="n">
         <v>127.9199981689453</v>
@@ -2759,7 +2759,7 @@
         <v>43799</v>
       </c>
       <c r="B83" t="n">
-        <v>112.7995834350586</v>
+        <v>112.7995681762695</v>
       </c>
       <c r="C83" t="n">
         <v>120.5199966430664</v>
@@ -2788,7 +2788,7 @@
         <v>43830</v>
       </c>
       <c r="B84" t="n">
-        <v>123.8717803955078</v>
+        <v>123.8717422485352</v>
       </c>
       <c r="C84" t="n">
         <v>132.3500061035156</v>
@@ -2817,7 +2817,7 @@
         <v>43861</v>
       </c>
       <c r="B85" t="n">
-        <v>125.7942199707031</v>
+        <v>125.7942123413086</v>
       </c>
       <c r="C85" t="n">
         <v>134.2100067138672</v>
@@ -2846,7 +2846,7 @@
         <v>43890</v>
       </c>
       <c r="B86" t="n">
-        <v>124.8756713867188</v>
+        <v>124.8756637573242</v>
       </c>
       <c r="C86" t="n">
         <v>133.2299957275391</v>
@@ -2875,7 +2875,7 @@
         <v>43921</v>
       </c>
       <c r="B87" t="n">
-        <v>110.3101196289062</v>
+        <v>110.3101272583008</v>
       </c>
       <c r="C87" t="n">
         <v>117.6900024414062</v>
@@ -2904,7 +2904,7 @@
         <v>43951</v>
       </c>
       <c r="B88" t="n">
-        <v>121.3976058959961</v>
+        <v>121.397575378418</v>
       </c>
       <c r="C88" t="n">
         <v>129.3099975585938</v>
@@ -2962,7 +2962,7 @@
         <v>44012</v>
       </c>
       <c r="B90" t="n">
-        <v>128.6545715332031</v>
+        <v>128.6546173095703</v>
       </c>
       <c r="C90" t="n">
         <v>137.0399932861328</v>
@@ -3049,7 +3049,7 @@
         <v>44104</v>
       </c>
       <c r="B93" t="n">
-        <v>155.4686584472656</v>
+        <v>155.4686279296875</v>
       </c>
       <c r="C93" t="n">
         <v>165.3699951171875</v>
@@ -3078,7 +3078,7 @@
         <v>44135</v>
       </c>
       <c r="B94" t="n">
-        <v>149.2435913085938</v>
+        <v>149.2435455322266</v>
       </c>
       <c r="C94" t="n">
         <v>158.5500030517578</v>
@@ -3107,7 +3107,7 @@
         <v>44165</v>
       </c>
       <c r="B95" t="n">
-        <v>150.9661254882812</v>
+        <v>150.9661560058594</v>
       </c>
       <c r="C95" t="n">
         <v>160.3800048828125</v>
@@ -3136,7 +3136,7 @@
         <v>44196</v>
       </c>
       <c r="B96" t="n">
-        <v>155.7855987548828</v>
+        <v>155.78564453125</v>
       </c>
       <c r="C96" t="n">
         <v>165.5</v>
@@ -3165,7 +3165,7 @@
         <v>44227</v>
       </c>
       <c r="B97" t="n">
-        <v>145.4209747314453</v>
+        <v>145.4209594726562</v>
       </c>
       <c r="C97" t="n">
         <v>154.25</v>
@@ -3194,7 +3194,7 @@
         <v>44255</v>
       </c>
       <c r="B98" t="n">
-        <v>146.3543243408203</v>
+        <v>146.3543090820312</v>
       </c>
       <c r="C98" t="n">
         <v>155.2400054931641</v>
@@ -3223,7 +3223,7 @@
         <v>44286</v>
       </c>
       <c r="B99" t="n">
-        <v>148.4660491943359</v>
+        <v>148.4661102294922</v>
       </c>
       <c r="C99" t="n">
         <v>157.4799957275391</v>
@@ -3252,7 +3252,7 @@
         <v>44316</v>
       </c>
       <c r="B100" t="n">
-        <v>163.3689727783203</v>
+        <v>163.3690185546875</v>
       </c>
       <c r="C100" t="n">
         <v>173.0299987792969</v>
@@ -3281,7 +3281,7 @@
         <v>44347</v>
       </c>
       <c r="B101" t="n">
-        <v>166.815185546875</v>
+        <v>166.8152160644531</v>
       </c>
       <c r="C101" t="n">
         <v>176.6799926757812</v>
@@ -3310,7 +3310,7 @@
         <v>44377</v>
       </c>
       <c r="B102" t="n">
-        <v>175.9547271728516</v>
+        <v>175.9547576904297</v>
       </c>
       <c r="C102" t="n">
         <v>186.3600006103516</v>
@@ -3339,7 +3339,7 @@
         <v>44408</v>
       </c>
       <c r="B103" t="n">
-        <v>191.6245574951172</v>
+        <v>191.6246032714844</v>
       </c>
       <c r="C103" t="n">
         <v>202.6999969482422</v>
@@ -3397,7 +3397,7 @@
         <v>44469</v>
       </c>
       <c r="B105" t="n">
-        <v>183.5323028564453</v>
+        <v>183.5322418212891</v>
       </c>
       <c r="C105" t="n">
         <v>194.1399993896484</v>
@@ -3426,7 +3426,7 @@
         <v>44500</v>
       </c>
       <c r="B106" t="n">
-        <v>204.6310424804688</v>
+        <v>204.6310119628906</v>
       </c>
       <c r="C106" t="n">
         <v>216.1999969482422</v>
@@ -3455,7 +3455,7 @@
         <v>44530</v>
       </c>
       <c r="B107" t="n">
-        <v>210.1585083007812</v>
+        <v>210.1584930419922</v>
       </c>
       <c r="C107" t="n">
         <v>222.0399932861328</v>
@@ -3484,7 +3484,7 @@
         <v>44561</v>
       </c>
       <c r="B108" t="n">
-        <v>230.9718627929688</v>
+        <v>230.9718322753906</v>
       </c>
       <c r="C108" t="n">
         <v>244.0299987792969</v>
@@ -3513,7 +3513,7 @@
         <v>44592</v>
       </c>
       <c r="B109" t="n">
-        <v>189.4028167724609</v>
+        <v>189.4028472900391</v>
       </c>
       <c r="C109" t="n">
         <v>199.7899932861328</v>
@@ -3542,7 +3542,7 @@
         <v>44620</v>
       </c>
       <c r="B110" t="n">
-        <v>183.58203125</v>
+        <v>183.5820465087891</v>
       </c>
       <c r="C110" t="n">
         <v>193.6499938964844</v>
@@ -3571,7 +3571,7 @@
         <v>44651</v>
       </c>
       <c r="B111" t="n">
-        <v>178.7851257324219</v>
+        <v>178.7851104736328</v>
       </c>
       <c r="C111" t="n">
         <v>188.5899963378906</v>
@@ -3600,7 +3600,7 @@
         <v>44681</v>
       </c>
       <c r="B112" t="n">
-        <v>168.3289031982422</v>
+        <v>168.3288879394531</v>
       </c>
       <c r="C112" t="n">
         <v>177.25</v>
@@ -3687,7 +3687,7 @@
         <v>44773</v>
       </c>
       <c r="B115" t="n">
-        <v>173.6802825927734</v>
+        <v>173.6803131103516</v>
       </c>
       <c r="C115" t="n">
         <v>182.5500030517578</v>
@@ -3716,7 +3716,7 @@
         <v>44804</v>
       </c>
       <c r="B116" t="n">
-        <v>148.9245452880859</v>
+        <v>148.9245758056641</v>
       </c>
       <c r="C116" t="n">
         <v>156.5299987792969</v>
@@ -3774,7 +3774,7 @@
         <v>44865</v>
       </c>
       <c r="B118" t="n">
-        <v>143.7587738037109</v>
+        <v>143.7587127685547</v>
       </c>
       <c r="C118" t="n">
         <v>150.7799987792969</v>
@@ -3803,7 +3803,7 @@
         <v>44895</v>
       </c>
       <c r="B119" t="n">
-        <v>146.9622802734375</v>
+        <v>146.9622955322266</v>
       </c>
       <c r="C119" t="n">
         <v>154.1399993896484</v>
@@ -3832,7 +3832,7 @@
         <v>44926</v>
       </c>
       <c r="B120" t="n">
-        <v>139.7257385253906</v>
+        <v>139.7257080078125</v>
       </c>
       <c r="C120" t="n">
         <v>146.5500030517578</v>
@@ -3890,7 +3890,7 @@
         <v>44985</v>
       </c>
       <c r="B122" t="n">
-        <v>159.5975799560547</v>
+        <v>159.5975646972656</v>
       </c>
       <c r="C122" t="n">
         <v>167</v>
@@ -3919,7 +3919,7 @@
         <v>45016</v>
       </c>
       <c r="B123" t="n">
-        <v>159.0624237060547</v>
+        <v>159.0623931884766</v>
       </c>
       <c r="C123" t="n">
         <v>166.4400024414062</v>
@@ -3948,7 +3948,7 @@
         <v>45046</v>
       </c>
       <c r="B124" t="n">
-        <v>168.3491668701172</v>
+        <v>168.3491821289062</v>
       </c>
       <c r="C124" t="n">
         <v>175.7799987792969</v>
@@ -3977,7 +3977,7 @@
         <v>45077</v>
       </c>
       <c r="B125" t="n">
-        <v>156.1189880371094</v>
+        <v>156.1190032958984</v>
       </c>
       <c r="C125" t="n">
         <v>163.0099945068359</v>
@@ -4064,7 +4064,7 @@
         <v>45169</v>
       </c>
       <c r="B128" t="n">
-        <v>182.8577423095703</v>
+        <v>182.8577270507812</v>
       </c>
       <c r="C128" t="n">
         <v>190.5099945068359</v>
@@ -4093,7 +4093,7 @@
         <v>45199</v>
       </c>
       <c r="B129" t="n">
-        <v>166.9917449951172</v>
+        <v>166.99169921875</v>
       </c>
       <c r="C129" t="n">
         <v>173.9799957275391</v>
@@ -4122,7 +4122,7 @@
         <v>45230</v>
       </c>
       <c r="B130" t="n">
-        <v>151.0545501708984</v>
+        <v>151.0545806884766</v>
       </c>
       <c r="C130" t="n">
         <v>157</v>
@@ -4180,7 +4180,7 @@
         <v>45291</v>
       </c>
       <c r="B132" t="n">
-        <v>189.8957672119141</v>
+        <v>189.895751953125</v>
       </c>
       <c r="C132" t="n">
         <v>197.3699951171875</v>
@@ -4209,7 +4209,7 @@
         <v>45322</v>
       </c>
       <c r="B133" t="n">
-        <v>181.1076354980469</v>
+        <v>181.107666015625</v>
       </c>
       <c r="C133" t="n">
         <v>187.8099975585938</v>
@@ -4238,7 +4238,7 @@
         <v>45351</v>
       </c>
       <c r="B134" t="n">
-        <v>191.2522430419922</v>
+        <v>191.2522277832031</v>
       </c>
       <c r="C134" t="n">
         <v>198.3300018310547</v>
@@ -4325,7 +4325,7 @@
         <v>45443</v>
       </c>
       <c r="B137" t="n">
-        <v>163.9751586914062</v>
+        <v>163.9751434326172</v>
       </c>
       <c r="C137" t="n">
         <v>169.5599975585938</v>
@@ -4354,7 +4354,7 @@
         <v>45473</v>
       </c>
       <c r="B138" t="n">
-        <v>167.6499786376953</v>
+        <v>167.6499633789062</v>
       </c>
       <c r="C138" t="n">
         <v>173.3600006103516</v>
@@ -4383,7 +4383,7 @@
         <v>45504</v>
       </c>
       <c r="B139" t="n">
-        <v>174.5241088867188</v>
+        <v>174.5241241455078</v>
       </c>
       <c r="C139" t="n">
         <v>180.0399932861328</v>
@@ -4441,7 +4441,7 @@
         <v>45565</v>
       </c>
       <c r="B141" t="n">
-        <v>189.3941497802734</v>
+        <v>189.3941345214844</v>
       </c>
       <c r="C141" t="n">
         <v>195.3800048828125</v>
@@ -4470,7 +4470,7 @@
         <v>45596</v>
       </c>
       <c r="B142" t="n">
-        <v>173.71337890625</v>
+        <v>173.7133483886719</v>
       </c>
       <c r="C142" t="n">
         <v>178.7799987792969</v>
@@ -4557,7 +4557,7 @@
         <v>45688</v>
       </c>
       <c r="B145" t="n">
-        <v>166.5587158203125</v>
+        <v>166.5587005615234</v>
       </c>
       <c r="C145" t="n">
         <v>170.8999938964844</v>
@@ -4673,7 +4673,7 @@
         <v>45808</v>
       </c>
       <c r="B149" t="n">
-        <v>164.9009399414062</v>
+        <v>164.9009704589844</v>
       </c>
       <c r="C149" t="n">
         <v>168.6300048828125</v>
@@ -4702,7 +4702,7 @@
         <v>45838</v>
       </c>
       <c r="B150" t="n">
-        <v>152.5013580322266</v>
+        <v>152.5013427734375</v>
       </c>
       <c r="C150" t="n">
         <v>155.9499969482422</v>
@@ -4760,7 +4760,7 @@
         <v>45900</v>
       </c>
       <c r="B152" t="n">
-        <v>153.4528045654297</v>
+        <v>153.4528198242188</v>
       </c>
       <c r="C152" t="n">
         <v>156.3999938964844</v>
@@ -4789,7 +4789,7 @@
         <v>45930</v>
       </c>
       <c r="B153" t="n">
-        <v>143.5627593994141</v>
+        <v>143.5627746582031</v>
       </c>
       <c r="C153" t="n">
         <v>146.3200073242188</v>
@@ -4876,7 +4876,7 @@
         <v>46022</v>
       </c>
       <c r="B156" t="n">
-        <v>123.8788986206055</v>
+        <v>123.8788909912109</v>
       </c>
       <c r="C156" t="n">
         <v>125.8199996948242</v>
